--- a/www/download/IND.hours_worked.empe_ms.r.pc.rpPE.xlsx
+++ b/www/download/IND.hours_worked.empe_ms.r.pc.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>0.464279231448657</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>0.456329998694853</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>0.451568568218632</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>0.449268730461982</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>44.72</t>
+          <t>0.447229005490679</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>44.39</t>
+          <t>0.443910519470523</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>0.440169407457856</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>0.433915692529417</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>0.42348566409138</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>0.441693523960817</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>0.453736060275888</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>0.451428220209313</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>0.448850642639693</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>0.44657341814401</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>0.444692000641331</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>69.21</t>
+          <t>0.692136262123675</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0.694001734582019</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>69.65</t>
+          <t>0.696494957489541</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>0.690772431517348</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>65.04</t>
+          <t>0.650369500307128</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>64.51</t>
+          <t>0.645128931342778</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>0.648318738386225</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>0.64230083574318</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>63.92</t>
+          <t>0.639248018015191</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>59.63</t>
+          <t>0.59625236404587</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>60.92</t>
+          <t>0.609186175393516</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>60.93</t>
+          <t>0.60931473642323</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>60.22</t>
+          <t>0.602169976307056</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>0.613982779927987</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>59.99</t>
+          <t>0.599900357011116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>54.48</t>
+          <t>0.544839067806272</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>0.547047365151056</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>55.05</t>
+          <t>0.55045635763286</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>55.53</t>
+          <t>0.555332791139806</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>56.06</t>
+          <t>0.560603380591902</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>0.570412628151096</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>57.64</t>
+          <t>0.576390168294394</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>0.578501547533332</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>57.63</t>
+          <t>0.57634864357822</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>0.584362856768334</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>0.588550630333424</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>0.591212951593434</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>0.587619370817737</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>0.560973091453563</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>0.560726850996046</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>0.257810155388644</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>0.262483109911152</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>0.253153617711366</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>0.247344634029229</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>0.269763750117847</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>0.279114814698076</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>0.28729365765645</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>0.282124417776103</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>0.263264598572064</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>0.280678248137305</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>0.277918201322617</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>0.283936834437297</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>0.270321088442263</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>0.262729373640372</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>0.278962492441108</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>0.379701644958971</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>0.386771809088146</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>0.396650595220496</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>0.409225994960821</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>42.14</t>
+          <t>0.421440882947612</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>0.432449658987846</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>0.44208377934465</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>44.91</t>
+          <t>0.44908706973155</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>44.97</t>
+          <t>0.449742710795738</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>0.46432386156275</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>0.472103304686085</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>0.471591521384643</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>0.470917224634245</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>0.471087795626342</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>0.47148135268107</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>71.36</t>
+          <t>0.713556904037973</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>0.710018482741305</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>0.705080719946882</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>0.694968760183561</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>69.93</t>
+          <t>0.699300324607141</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>68.96</t>
+          <t>0.689638448954784</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>0.681129793127399</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>67.55</t>
+          <t>0.675512232657553</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>67.06</t>
+          <t>0.67057249392285</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>66.71</t>
+          <t>0.667147634544804</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>65.59</t>
+          <t>0.655941115502853</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>64.43</t>
+          <t>0.644256988109137</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>0.636360147916191</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>0.641173453945161</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>0.623028705044523</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>58.74</t>
+          <t>0.587435557295619</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>0.585323919296318</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>58.64</t>
+          <t>0.586431178012191</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>0.59124104144537</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>59.49</t>
+          <t>0.594850137508196</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>59.78</t>
+          <t>0.597752487402108</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>59.84</t>
+          <t>0.598445726108527</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>59.66</t>
+          <t>0.596550085875239</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>0.570739614142451</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>56.45</t>
+          <t>0.56446285420335</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>54.21</t>
+          <t>0.542091879357631</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>0.519725681457969</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>0.517184213965928</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>0.505487916857416</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>50.42</t>
+          <t>0.504163493409673</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>0.348159438487842</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>0.350791303722316</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>0.348628315544066</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>0.346776855493985</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>36.72</t>
+          <t>0.367228702692849</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>0.365108731851971</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>0.36395074825005</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>0.356912062558847</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>0.358449735647864</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>0.373252046723813</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>0.392121724222384</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>0.398425952750391</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>0.382822896476434</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>38.32</t>
+          <t>0.383175701757355</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>0.377118085097003</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>77.53</t>
+          <t>0.775258934872724</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>77.26</t>
+          <t>0.77256008446739</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.11</t>
+          <t>0.771145438454611</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76.94</t>
+          <t>0.769413961659692</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76.62</t>
+          <t>0.766237531325325</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>0.762495452665945</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>76.07</t>
+          <t>0.760712345028576</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>75.52</t>
+          <t>0.755223535194773</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>75.53</t>
+          <t>0.755258973242011</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>0.746797113968613</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>0.746976424801815</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>0.740170647870372</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>0.741844249607334</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>0.732422152224287</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>0.713063875678945</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>0.57693560024983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>57.26</t>
+          <t>0.572555235133934</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>56.93</t>
+          <t>0.56926048783253</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>55.24</t>
+          <t>0.552366159608321</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>0.553008463456542</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>54.89</t>
+          <t>0.548897364458009</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>54.36</t>
+          <t>0.543614752086095</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>53.72</t>
+          <t>0.537243832003836</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>0.517849596137025</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>51.41</t>
+          <t>0.514101396075194</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.513471839569796</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>0.521073369740453</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>0.532734731351301</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>52.85</t>
+          <t>0.528467973827193</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>51.04</t>
+          <t>0.510374114149488</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>54.11</t>
+          <t>0.541098424426635</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.26</t>
+          <t>0.532604949963745</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>52.58</t>
+          <t>0.525830143593215</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>0.518675092837624</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>51.75</t>
+          <t>0.517525366855509</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>51.69</t>
+          <t>0.516940311525733</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>51.07</t>
+          <t>0.510703384299418</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>0.503597342352725</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>45.72</t>
+          <t>0.457158317443853</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>0.454440807107213</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>0.436657178133145</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>0.431044951120532</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>0.42942763318421</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>0.411131187279948</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>39.71</t>
+          <t>0.397101175434395</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>0.206890735754316</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>0.208497526577858</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>0.214584050460499</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213599178388591</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>0.215612572954155</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>0.212142590032889</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>0.208744709413346</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>0.206556563835731</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>0.205146379332471</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>0.21140452585859</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>0.218895487693063</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>0.22059498223511</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>0.221202643349471</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>0.220580621626342</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>0.212471156690214</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>0.462666400171939</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.62</t>
+          <t>0.466155508831543</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>0.468137110543704</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>46.92</t>
+          <t>0.469170640844596</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>0.487766779168706</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>0.480264033295526</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>0.477604993455266</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>0.469555360327549</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>0.473499092808326</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>0.456971641687718</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>0.44200789719352</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0.442623891471561</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>0.44867691427692</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>0.444230451844586</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>0.432221631024717</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>0.397746460379845</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>39.34</t>
+          <t>0.393415215635403</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>0.393332595256746</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>0.392439704199376</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.394691177067126</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>0.397189499444468</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>0.397270319600905</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>0.39627506567836</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>0.395331841818262</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>0.396227112676555</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>0.397605034546096</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>0.399273107287266</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>0.396190239659514</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>0.394414804484384</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>0.378085673151558</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>0.47313368585565</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.39</t>
+          <t>0.463891315813491</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>0.460337011404009</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>0.458126687667002</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>0.452352411348916</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45.18</t>
+          <t>0.451767929250298</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>44.94</t>
+          <t>0.449396131153625</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>0.44889471578271</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>0.446000614659444</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>0.44153272756888</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>0.430395584891182</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>0.414989185316598</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>0.416197351238902</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>0.41466285712297</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>0.39206096872691</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>0.457279993700631</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>0.459393574794474</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0.461954842970425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>0.448983700889684</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>0.439267480932206</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>42.37</t>
+          <t>0.423690737963282</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>0.413788275424887</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>0.409041441484572</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>0.418682668219485</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>0.43314327415062</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>0.429765303165532</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>0.420428640084679</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>0.396866272014268</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>0.398962194231892</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>39.74</t>
+          <t>0.397366737323158</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>0.426691856801175</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>0.425336402296975</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>0.434470549133028</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>0.444856160022776</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>0.473152081022962</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.470037517585314</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>0.471102157724361</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>0.47311058526041</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>0.470251972534385</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>0.474144625730802</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>47.94</t>
+          <t>0.479385539972153</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>0.435948320481257</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>0.43043330818275</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>0.434295003619091</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>42.91</t>
+          <t>0.429108650186043</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>0.677833029426623</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>67.44</t>
+          <t>0.674376320083935</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>67.28</t>
+          <t>0.672798001422632</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>67.15</t>
+          <t>0.671485645437709</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>66.59</t>
+          <t>0.665854820615166</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>66.72</t>
+          <t>0.667233439760036</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>66.83</t>
+          <t>0.668267932176083</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>0.668028192579496</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>65.75</t>
+          <t>0.657531004032354</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>63.97</t>
+          <t>0.639736854372774</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>63.21</t>
+          <t>0.632103324901836</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>63.08</t>
+          <t>0.630777419055233</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>0.633750410534317</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>61.06</t>
+          <t>0.610607396856165</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>0.610259375190225</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>0.363289048460441</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>0.368342579800386</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>0.378515237420934</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>0.39013019288613</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>0.392324537802222</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0.41292248011023</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>0.405936711107561</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>0.407026032193136</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>42.44</t>
+          <t>0.424362303673971</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>0.416226022790541</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>0.41376976311674</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>0.410139958617995</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>0.394021871918884</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>0.389293850309577</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>0.388455420208187</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>0.477421320575452</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>0.478000622806635</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>48.18</t>
+          <t>0.481753853650408</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>0.488299635922274</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>49.51</t>
+          <t>0.495083337002571</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>0.484107127101319</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>47.29</t>
+          <t>0.472888001785081</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.459951296123359</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>0.440913241052009</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>0.435599540970021</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>0.434450759157723</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>0.431876180798955</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>0.428698014983939</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>42.61</t>
+          <t>0.426071909389533</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>0.424337408586454</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>0.463420293025284</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>0.4569538738121</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>0.458921369891313</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>0.446062536300017</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>0.436235144284739</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>0.427586229572999</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>0.416389091978472</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>0.400064777579699</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>0.380624895829739</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>0.362249986560056</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>0.359531711464897</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>0.348680834223054</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>0.342526141666748</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>0.33132074864256</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>0.312944427854261</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>51.84</t>
+          <t>0.518415739989673</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>0.5224707764689</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>52.99</t>
+          <t>0.529862111298327</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>54.07</t>
+          <t>0.540654589776039</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>0.542939974195064</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>0.562572363727912</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>54.18</t>
+          <t>0.541800047370739</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>0.538211116140977</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>0.533214085905601</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>0.567059704849897</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>0.554462446684503</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>54.69</t>
+          <t>0.546885120129465</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>53.77</t>
+          <t>0.537677311776539</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>52.09</t>
+          <t>0.520949030650714</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>0.531954970488271</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>0.579479185858004</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>0.573088198986263</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>0.569186802462386</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>56.07</t>
+          <t>0.560689239369208</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>55.65</t>
+          <t>0.556463689335333</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>0.552015854929772</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>54.51</t>
+          <t>0.54507492657662</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>0.534847739951375</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>0.535379243377685</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>53.39</t>
+          <t>0.533923586119178</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>0.535350659287623</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>0.5350163957751</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>53.72</t>
+          <t>0.537151580968896</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>53.81</t>
+          <t>0.538115106113555</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>53.51</t>
+          <t>0.535107659757911</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>0.424574244597512</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>40.81</t>
+          <t>0.408145915869746</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>0.402526281589052</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>0.380195621129563</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>0.370449763882189</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>0.374331063866811</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>0.366051586986448</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>0.338171674747706</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>33.22</t>
+          <t>0.332198648496284</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>0.332473534197742</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>0.325332165676898</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>32.52</t>
+          <t>0.325173398982889</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>0.327517888494781</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>0.328669477859984</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>0.325789630639009</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>0.533195858273454</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>0.536466799619575</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>53.92</t>
+          <t>0.539169852517655</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>0.540934807250721</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>55.74</t>
+          <t>0.557361362849752</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>55.19</t>
+          <t>0.55194435073716</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0.549960755868425</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>0.542033809430307</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>0.521658985016304</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>0.522657392183035</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>51.12</t>
+          <t>0.511183992718785</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>0.50845992883912</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>48.96</t>
+          <t>0.489568674628268</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>0.487523074893578</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>0.470849731791764</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>0.371013400867023</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>0.392818086636793</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>43.57</t>
+          <t>0.435742667476969</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>0.477618943995236</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>0.516070578672614</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>0.51107769085204</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>0.506461412728394</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>0.502443078505028</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>0.547447374056262</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>0.458365100591473</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>0.445161645992726</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>47.07</t>
+          <t>0.470716283745523</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>0.444522415158776</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>0.456082662077969</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>0.415438337810893</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>0.562521111693676</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>0.565682391198161</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>0.567218497292639</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>0.568009318772836</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>58.58</t>
+          <t>0.585814919447807</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>58.11</t>
+          <t>0.581075496522912</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>0.57970133894929</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>0.573147532721349</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>0.597462167040276</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>0.571475765991542</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>0.590657509082585</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>0.581564132653749</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>55.36</t>
+          <t>0.553602460515238</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>0.51801934146222</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>0.524007553996848</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>46.01</t>
+          <t>0.46014023018794</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>0.458946912037483</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>47.79</t>
+          <t>0.477865530877826</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>0.474172279331286</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>0.475674035485452</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>0.475017083365576</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>48.69</t>
+          <t>0.486863035389145</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>48.97</t>
+          <t>0.489721749380123</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>0.490791893225511</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>0.503786018032453</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>50.76</t>
+          <t>0.507640606052541</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>0.518842947320539</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>51.76</t>
+          <t>0.51756215160456</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>0.516183970988844</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>51.39</t>
+          <t>0.513925630369174</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>0.257810155388644</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>0.262483109911152</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>0.253153617711366</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>0.247344634029229</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>0.269763750117847</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>0.279114814698076</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>0.28729365765645</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>0.282124417776103</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>0.263264598572064</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>0.280678248137305</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>0.277918201322617</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>0.283936834437297</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>0.270321088442263</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>0.262729373640372</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>0.278962492441108</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>0.5297152979985</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>0.515007587784185</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>0.490314699813863</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>0.493061977630724</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>0.469085409961667</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>0.466896056700721</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>47.58</t>
+          <t>0.475762622298776</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>0.466115899480994</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>0.431875006854593</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>0.417463463388115</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>0.415071549454945</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>0.416303565639539</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>42.14</t>
+          <t>0.421354383847686</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>0.401867634528623</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>0.393344668862463</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>0.738214004538825</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>0.735265992140505</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>73.37</t>
+          <t>0.733703991301743</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>73.17</t>
+          <t>0.731746645630096</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>73.19</t>
+          <t>0.731938709783092</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>0.730619644632224</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>71.18</t>
+          <t>0.711806889727962</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>0.699592076531764</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>67.66</t>
+          <t>0.676597236325638</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>0.649322803358627</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>0.637096924283515</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>62.77</t>
+          <t>0.627663619543683</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>62.28</t>
+          <t>0.622761087107021</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>61.75</t>
+          <t>0.617509498654693</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>0.59211372593074</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>0.257810155388644</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>0.262483109911152</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>0.253153617711366</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>0.247344634029229</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>0.269763750117847</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>0.279114814698076</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>0.28729365765645</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>0.282124417776103</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>0.263264598572064</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>0.280678248137305</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>0.277918201322617</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>0.283936834437297</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>0.270321088442263</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>0.262729373640372</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>0.278962492441108</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>0.257810155388644</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>0.262483109911152</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>0.253153617711366</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>0.247344634029229</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>0.269763750117847</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>0.279114814698076</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>0.28729365765645</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>0.282124417776103</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>0.263264598572064</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>0.280678248137305</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>0.277918201322617</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>0.283936834437297</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>0.270321088442263</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>0.262729373640372</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>0.278962492441108</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>0.754175230091266</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>75.16</t>
+          <t>0.751558994555753</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>75.02</t>
+          <t>0.750231024341683</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>0.748722733810512</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>74.54</t>
+          <t>0.745448012458926</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>0.741960586816535</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>74.04</t>
+          <t>0.740369533550678</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>0.734947228636935</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>0.731183627120109</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>73.11</t>
+          <t>0.731145168907696</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>0.729135516660194</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>0.72875342047666</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>0.729957904978536</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>73.04</t>
+          <t>0.730416641995585</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>0.728323186282626</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>0.761018978432762</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>75.82</t>
+          <t>0.758208477893555</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>75.67</t>
+          <t>0.75669773977327</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>75.47</t>
+          <t>0.754746817954443</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>0.772652331718268</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>77.25</t>
+          <t>0.772454078534314</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>76.84</t>
+          <t>0.768374761948287</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>0.771529906898114</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>76.01</t>
+          <t>0.760090235118038</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>0.753799212567407</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>73.36</t>
+          <t>0.733629923810431</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>0.72388982961556</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>72.71</t>
+          <t>0.727075453630007</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>0.726728257211577</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>0.714540926308686</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>65.53</t>
+          <t>0.655324200183364</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>65.17</t>
+          <t>0.651728999403955</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>65.01</t>
+          <t>0.650055981084126</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>64.86</t>
+          <t>0.648571980808518</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>64.57</t>
+          <t>0.64569693789155</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>0.626225856069102</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>67.13</t>
+          <t>0.671269782751062</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>64.76</t>
+          <t>0.647577418796372</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>61.62</t>
+          <t>0.616184007658355</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>0.60625893911699</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>0.600388113780016</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>0.589828851294912</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>0.585343830685459</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>0.572356289553705</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>55.08</t>
+          <t>0.550766089779198</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>62.89</t>
+          <t>0.628896494752263</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>62.63</t>
+          <t>0.626299336558315</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>62.36</t>
+          <t>0.623602503981912</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>0.622009725421366</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>60.91</t>
+          <t>0.609076743244502</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>0.595456477809172</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>58.95</t>
+          <t>0.589487448701118</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>58.19</t>
+          <t>0.581852789921171</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>0.577180461179477</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>56.97</t>
+          <t>0.569738366000258</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>0.555877696016183</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>54.04</t>
+          <t>0.540381517747279</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>53.76</t>
+          <t>0.537629126752471</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>0.522725725181267</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>0.491705715792688</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>0.322056169090658</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>0.3275279635697</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>0.320652020130678</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>0.340933115891918</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>0.335876779021776</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>0.345229314455496</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>0.349183866020192</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>0.347573336367733</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>0.340057457113966</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>0.356324595721226</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>0.353504077027458</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>0.3480639639186</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>0.349186542757386</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>0.348525578248511</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>0.349616919058489</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>0.351722960932724</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>0.347799936892726</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>0.346522438291578</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>0.346356021976855</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>0.347921635768772</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>0.348160340861764</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>0.349437055743162</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>0.349254559164153</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>0.342293103752778</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>34.31</t>
+          <t>0.343114552690408</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>0.335864945710607</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>0.325000720481674</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>0.328402543472943</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>0.320389142844897</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>0.308782001100256</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>56.55</t>
+          <t>0.565478329346987</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>56.42</t>
+          <t>0.564176393713312</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>55.67</t>
+          <t>0.556656109053554</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>0.550282156578555</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>54.74</t>
+          <t>0.547415026399317</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>54.42</t>
+          <t>0.544159921790481</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>0.537108627190405</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>53.04</t>
+          <t>0.530415341339099</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>53.36</t>
+          <t>0.533632613460725</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>52.55</t>
+          <t>0.525545942065996</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>52.42</t>
+          <t>0.524216288005377</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>0.519009613481332</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>52.34</t>
+          <t>0.523444785120323</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>0.519561219106608</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>50.88</t>
+          <t>0.508791117275826</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>51.75</t>
+          <t>0.517495238072068</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>51.48</t>
+          <t>0.514792904979893</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>51.45</t>
+          <t>0.514543351153794</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>0.513626584238275</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>51.58</t>
+          <t>0.515791118359541</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>51.33</t>
+          <t>0.51334135461801</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>51.16</t>
+          <t>0.51159528127531</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>0.504985460600167</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>0.496308413497245</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>0.492094445939373</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>0.487827871064791</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>0.483218902241029</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>0.477981212518004</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>0.471663517215407</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>0.4621224817634</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>0.495962224056606</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>0.495177705640178</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>0.495207742863055</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>0.494705048720725</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>0.498411357729967</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>49.78</t>
+          <t>0.497772510097792</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>0.49698514072938</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>0.491421137969348</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>0.484092944743028</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>0.481252008673121</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>0.478117596950705</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>47.46</t>
+          <t>0.474587733899196</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>0.469524828353946</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>46.36</t>
+          <t>0.463588267617551</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>0.45639004331361</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
